--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化.xlsx
@@ -421,7 +421,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.42578125" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -484,28 +484,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>603.14869999999996</v>
+        <v>606.4973</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>19.809606492013078</v>
+        <v>19.842236501118745</v>
       </c>
       <c r="F2" s="0">
-        <v>-3.1903935079869221</v>
+        <v>-3.1577634988812555</v>
       </c>
       <c r="G2" s="0">
-        <v>3.1903935079869221</v>
+        <v>3.1577634988812555</v>
       </c>
       <c r="H2" s="0">
-        <v>19.309606492013078</v>
+        <v>19.342236501118745</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.6903935079869221</v>
+        <v>-3.6577634988812555</v>
       </c>
       <c r="J2" s="0">
-        <v>3.6903935079869221</v>
+        <v>3.6577634988812555</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -528,28 +528,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>609.20730000000003</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.103177685576643</v>
+        <v>20.090406914195555</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.89682231442335692</v>
+        <v>-0.90959308580444542</v>
       </c>
       <c r="G3" s="0">
-        <v>0.89682231442335692</v>
+        <v>0.90959308580444542</v>
       </c>
       <c r="H3" s="0">
-        <v>19.603177685576643</v>
+        <v>19.590406914195555</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.3968223144233569</v>
+        <v>-1.4095930858044454</v>
       </c>
       <c r="J3" s="0">
-        <v>1.3968223144233569</v>
+        <v>1.4095930858044454</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -572,28 +572,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>755.06500000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.295794706207026</v>
+        <v>23.107745147697024</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.20420529379297392</v>
+        <v>-0.39225485230297608</v>
       </c>
       <c r="G4" s="0">
-        <v>0.20420529379297392</v>
+        <v>0.39225485230297608</v>
       </c>
       <c r="H4" s="0">
-        <v>22.795794706207026</v>
+        <v>22.607745147697024</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.70420529379297392</v>
+        <v>-0.89225485230297608</v>
       </c>
       <c r="J4" s="0">
-        <v>0.70420529379297392</v>
+        <v>0.89225485230297608</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -616,28 +616,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>579.86080000000004</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.644628447932277</v>
+        <v>19.604443642841563</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.355371552067723</v>
+        <v>-1.3955563571584371</v>
       </c>
       <c r="G5" s="0">
-        <v>1.355371552067723</v>
+        <v>1.3955563571584371</v>
       </c>
       <c r="H5" s="0">
-        <v>19.144628447932277</v>
+        <v>19.104443642841563</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.855371552067723</v>
+        <v>-1.8955563571584371</v>
       </c>
       <c r="J5" s="0">
-        <v>1.855371552067723</v>
+        <v>1.8955563571584371</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -660,28 +660,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>634.26990000000001</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.565961984121199</v>
+        <v>20.511320650915728</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.93403801587880153</v>
+        <v>-0.98867934908427202</v>
       </c>
       <c r="G6" s="0">
-        <v>0.93403801587880153</v>
+        <v>0.98867934908427202</v>
       </c>
       <c r="H6" s="0">
-        <v>20.065961984121199</v>
+        <v>20.011320650915728</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.4340380158788015</v>
+        <v>-1.488679349084272</v>
       </c>
       <c r="J6" s="0">
-        <v>1.4340380158788015</v>
+        <v>1.488679349084272</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -704,31 +704,31 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>691.86599999999999</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>22.664792365195705</v>
+        <v>21.636806640470915</v>
       </c>
       <c r="F7" s="0">
-        <v>0.66479236519570506</v>
+        <v>-0.3631933595290846</v>
       </c>
       <c r="G7" s="0">
-        <v>0.66479236519570506</v>
+        <v>0.3631933595290846</v>
       </c>
       <c r="H7" s="0">
-        <v>22.164792365195705</v>
+        <v>21.136806640470915</v>
       </c>
       <c r="I7" s="0">
-        <v>0.16479236519570506</v>
+        <v>-0.8631933595290846</v>
       </c>
       <c r="J7" s="0">
-        <v>0.16479236519570506</v>
+        <v>0.8631933595290846</v>
       </c>
       <c r="K7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
         <v>5</v>
@@ -748,28 +748,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>763.82230000000004</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.144999573343739</v>
+        <v>23.573508183523323</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.855000426656261</v>
+        <v>-1.4264918164766769</v>
       </c>
       <c r="G8" s="0">
-        <v>1.855000426656261</v>
+        <v>1.4264918164766769</v>
       </c>
       <c r="H8" s="0">
-        <v>22.644999573343739</v>
+        <v>23.073508183523323</v>
       </c>
       <c r="I8" s="0">
-        <v>-2.355000426656261</v>
+        <v>-1.9264918164766769</v>
       </c>
       <c r="J8" s="0">
-        <v>2.355000426656261</v>
+        <v>1.9264918164766769</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -792,28 +792,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>607.71310000000005</v>
+        <v>612.55169999999998</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.135702067204086</v>
+        <v>20.140202468328937</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.36429793279591394</v>
+        <v>-0.3597975316710631</v>
       </c>
       <c r="G9" s="0">
-        <v>0.36429793279591394</v>
+        <v>0.3597975316710631</v>
       </c>
       <c r="H9" s="0">
-        <v>19.635702067204086</v>
+        <v>19.640202468328937</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.86429793279591394</v>
+        <v>-0.8597975316710631</v>
       </c>
       <c r="J9" s="0">
-        <v>0.86429793279591394</v>
+        <v>0.8597975316710631</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -836,28 +836,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>641.99860000000001</v>
+        <v>647.83249999999998</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>20.768367090812703</v>
+        <v>20.787880293704873</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.23163290918729729</v>
+        <v>-0.21211970629512678</v>
       </c>
       <c r="G10" s="0">
-        <v>0.23163290918729729</v>
+        <v>0.21211970629512678</v>
       </c>
       <c r="H10" s="0">
-        <v>20.268367090812703</v>
+        <v>20.287880293704873</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.73163290918729729</v>
+        <v>-0.71211970629512678</v>
       </c>
       <c r="J10" s="0">
-        <v>0.73163290918729729</v>
+        <v>0.71211970629512678</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -880,28 +880,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>463.59699999999998</v>
+        <v>468.75369999999998</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.394392728946443</v>
+        <v>19.586004925704792</v>
       </c>
       <c r="F11" s="0">
-        <v>2.3943927289464426</v>
+        <v>1.5860049257047919</v>
       </c>
       <c r="G11" s="0">
-        <v>2.3943927289464426</v>
+        <v>1.5860049257047919</v>
       </c>
       <c r="H11" s="0">
-        <v>19.894392728946443</v>
+        <v>19.086004925704792</v>
       </c>
       <c r="I11" s="0">
-        <v>1.8943927289464426</v>
+        <v>1.0860049257047919</v>
       </c>
       <c r="J11" s="0">
-        <v>1.8943927289464426</v>
+        <v>1.0860049257047919</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -924,28 +924,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>745.02800000000002</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>23.26526770657221</v>
+        <v>23.14196628846112</v>
       </c>
       <c r="F12" s="0">
-        <v>-1.7347322934277898</v>
+        <v>-1.8580337115388801</v>
       </c>
       <c r="G12" s="0">
-        <v>1.7347322934277898</v>
+        <v>1.8580337115388801</v>
       </c>
       <c r="H12" s="0">
-        <v>22.76526770657221</v>
+        <v>22.64196628846112</v>
       </c>
       <c r="I12" s="0">
-        <v>-2.2347322934277898</v>
+        <v>-2.3580337115388801</v>
       </c>
       <c r="J12" s="0">
-        <v>2.2347322934277898</v>
+        <v>2.3580337115388801</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -968,28 +968,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>674.10310000000004</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.595020697501862</v>
+        <v>21.487994294786844</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.90497930249813763</v>
+        <v>-1.0120057052131557</v>
       </c>
       <c r="G13" s="0">
-        <v>0.90497930249813763</v>
+        <v>1.0120057052131557</v>
       </c>
       <c r="H13" s="0">
-        <v>21.095020697501862</v>
+        <v>20.987994294786844</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.4049793024981376</v>
+        <v>-1.5120057052131557</v>
       </c>
       <c r="J13" s="0">
-        <v>1.4049793024981376</v>
+        <v>1.5120057052131557</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1012,28 +1012,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>678.64329999999995</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.445470557636234</v>
+        <v>21.376831548872094</v>
       </c>
       <c r="F14" s="0">
-        <v>0.94547055763623433</v>
+        <v>0.87683154887209369</v>
       </c>
       <c r="G14" s="0">
-        <v>0.94547055763623433</v>
+        <v>0.87683154887209369</v>
       </c>
       <c r="H14" s="0">
-        <v>20.945470557636234</v>
+        <v>20.876831548872094</v>
       </c>
       <c r="I14" s="0">
-        <v>0.44547055763623433</v>
+        <v>0.37683154887209369</v>
       </c>
       <c r="J14" s="0">
-        <v>0.44547055763623433</v>
+        <v>0.37683154887209369</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1056,28 +1056,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>588.29200000000003</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>19.632733935989595</v>
+        <v>19.673175069373656</v>
       </c>
       <c r="F15" s="0">
-        <v>0.13273393598959515</v>
+        <v>0.17317506937365579</v>
       </c>
       <c r="G15" s="0">
-        <v>0.13273393598959515</v>
+        <v>0.17317506937365579</v>
       </c>
       <c r="H15" s="0">
-        <v>19.132733935989595</v>
+        <v>19.173175069373656</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.36726606401040485</v>
+        <v>-0.32682493062634421</v>
       </c>
       <c r="J15" s="0">
-        <v>0.36726606401040485</v>
+        <v>0.32682493062634421</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>0</v>
@@ -1100,28 +1100,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.86260000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>20.289622506323102</v>
+        <v>20.239344029463112</v>
       </c>
       <c r="F16" s="0">
-        <v>0.78962250632310216</v>
+        <v>0.73934402946311195</v>
       </c>
       <c r="G16" s="0">
-        <v>0.78962250632310216</v>
+        <v>0.73934402946311195</v>
       </c>
       <c r="H16" s="0">
-        <v>19.789622506323102</v>
+        <v>19.739344029463112</v>
       </c>
       <c r="I16" s="0">
-        <v>0.28962250632310216</v>
+        <v>0.23934402946311195</v>
       </c>
       <c r="J16" s="0">
-        <v>0.28962250632310216</v>
+        <v>0.23934402946311195</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1144,28 +1144,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>565.14229999999998</v>
+        <v>557.87480000000005</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.597902605283156</v>
+        <v>19.552710564108011</v>
       </c>
       <c r="F17" s="0">
-        <v>1.0979026052831564</v>
+        <v>1.0527105641080112</v>
       </c>
       <c r="G17" s="0">
-        <v>1.0979026052831564</v>
+        <v>1.0527105641080112</v>
       </c>
       <c r="H17" s="0">
-        <v>19.097902605283156</v>
+        <v>19.052710564108011</v>
       </c>
       <c r="I17" s="0">
-        <v>0.59790260528315642</v>
+        <v>0.55271056410801123</v>
       </c>
       <c r="J17" s="0">
-        <v>0.59790260528315642</v>
+        <v>0.55271056410801123</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1188,28 +1188,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>726.14229999999998</v>
+        <v>734.02059999999995</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>22.775972404957763</v>
+        <v>22.90277258058093</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.97402759504223724</v>
+        <v>-0.84722741941907032</v>
       </c>
       <c r="G18" s="0">
-        <v>0.97402759504223724</v>
+        <v>0.84722741941907032</v>
       </c>
       <c r="H18" s="0">
-        <v>22.275972404957763</v>
+        <v>22.40277258058093</v>
       </c>
       <c r="I18" s="0">
-        <v>-1.4740275950422372</v>
+        <v>-1.3472274194190703</v>
       </c>
       <c r="J18" s="0">
-        <v>1.4740275950422372</v>
+        <v>1.3472274194190703</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1232,28 +1232,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>674.8356</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.121931338072532</v>
+        <v>20.916699364719882</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.1280686619274683</v>
+        <v>-1.3333006352801178</v>
       </c>
       <c r="G19" s="0">
-        <v>1.1280686619274683</v>
+        <v>1.3333006352801178</v>
       </c>
       <c r="H19" s="0">
-        <v>20.621931338072532</v>
+        <v>20.416699364719882</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.6280686619274682</v>
+        <v>-1.8333006352801178</v>
       </c>
       <c r="J19" s="0">
-        <v>1.6280686619274682</v>
+        <v>1.8333006352801178</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1276,28 +1276,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>758.93589999999995</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.243138866224143</v>
+        <v>23.347195010719474</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.2568611337758569</v>
+        <v>-2.1528049892805257</v>
       </c>
       <c r="G20" s="0">
-        <v>2.2568611337758569</v>
+        <v>2.1528049892805257</v>
       </c>
       <c r="H20" s="0">
-        <v>22.743138866224143</v>
+        <v>22.847195010719474</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.7568611337758569</v>
+        <v>-2.6528049892805257</v>
       </c>
       <c r="J20" s="0">
-        <v>2.7568611337758569</v>
+        <v>2.6528049892805257</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1320,28 +1320,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>526.39779999999996</v>
+        <v>530.03160000000003</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>18.857655878836482</v>
+        <v>18.876228640577274</v>
       </c>
       <c r="F21" s="0">
-        <v>-3.6423441211635179</v>
+        <v>-3.6237713594227259</v>
       </c>
       <c r="G21" s="0">
-        <v>3.6423441211635179</v>
+        <v>3.6237713594227259</v>
       </c>
       <c r="H21" s="0">
-        <v>18.357655878836482</v>
+        <v>18.376228640577274</v>
       </c>
       <c r="I21" s="0">
-        <v>-4.1423441211635179</v>
+        <v>-4.1237713594227259</v>
       </c>
       <c r="J21" s="0">
-        <v>4.1423441211635179</v>
+        <v>4.1237713594227259</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1364,28 +1364,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>619.3691</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.464688920418659</v>
+        <v>20.301415660704343</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.0353110795813407</v>
+        <v>-1.1985843392956568</v>
       </c>
       <c r="G22" s="0">
-        <v>1.0353110795813407</v>
+        <v>1.1985843392956568</v>
       </c>
       <c r="H22" s="0">
-        <v>19.964688920418659</v>
+        <v>19.801415660704343</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.5353110795813407</v>
+        <v>-1.6985843392956568</v>
       </c>
       <c r="J22" s="0">
-        <v>1.5353110795813407</v>
+        <v>1.6985843392956568</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1408,28 +1408,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>681.04340000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.386824023540342</v>
+        <v>21.427805265640963</v>
       </c>
       <c r="F23" s="0">
-        <v>1.386824023540342</v>
+        <v>1.4278052656409628</v>
       </c>
       <c r="G23" s="0">
-        <v>1.386824023540342</v>
+        <v>1.4278052656409628</v>
       </c>
       <c r="H23" s="0">
-        <v>20.886824023540342</v>
+        <v>20.927805265640963</v>
       </c>
       <c r="I23" s="0">
-        <v>0.88682402354034196</v>
+        <v>0.92780526564096277</v>
       </c>
       <c r="J23" s="0">
-        <v>0.88682402354034196</v>
+        <v>0.92780526564096277</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1452,28 +1452,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>585.4384</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.791973918358579</v>
+        <v>19.786843584350411</v>
       </c>
       <c r="F24" s="0">
-        <v>0.291973918358579</v>
+        <v>0.28684358435041091</v>
       </c>
       <c r="G24" s="0">
-        <v>0.291973918358579</v>
+        <v>0.28684358435041091</v>
       </c>
       <c r="H24" s="0">
-        <v>19.291973918358579</v>
+        <v>19.286843584350411</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.208026081641421</v>
+        <v>-0.21315641564958909</v>
       </c>
       <c r="J24" s="0">
-        <v>0.208026081641421</v>
+        <v>0.21315641564958909</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1496,28 +1496,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>581.173</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.796239314551141</v>
+        <v>19.543219559556985</v>
       </c>
       <c r="F25" s="0">
-        <v>1.2962393145511406</v>
+        <v>1.0432195595569844</v>
       </c>
       <c r="G25" s="0">
-        <v>1.2962393145511406</v>
+        <v>1.0432195595569844</v>
       </c>
       <c r="H25" s="0">
-        <v>19.296239314551141</v>
+        <v>19.043219559556985</v>
       </c>
       <c r="I25" s="0">
-        <v>0.79623931455114061</v>
+        <v>0.54321955955698442</v>
       </c>
       <c r="J25" s="0">
-        <v>0.79623931455114061</v>
+        <v>0.54321955955698442</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1540,28 +1540,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>692.99239999999998</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>21.929389489424356</v>
+        <v>21.94346003127864</v>
       </c>
       <c r="F26" s="0">
-        <v>0.67938948942435573</v>
+        <v>0.69346003127864009</v>
       </c>
       <c r="G26" s="0">
-        <v>0.67938948942435573</v>
+        <v>0.69346003127864009</v>
       </c>
       <c r="H26" s="0">
-        <v>21.429389489424356</v>
+        <v>21.44346003127864</v>
       </c>
       <c r="I26" s="0">
-        <v>0.17938948942435573</v>
+        <v>0.19346003127864009</v>
       </c>
       <c r="J26" s="0">
-        <v>0.17938948942435573</v>
+        <v>0.19346003127864009</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1584,28 +1584,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>643.06439999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.811086969560673</v>
+        <v>20.686636276861059</v>
       </c>
       <c r="F27" s="0">
-        <v>1.5610869695606731</v>
+        <v>1.4366362768610586</v>
       </c>
       <c r="G27" s="0">
-        <v>1.5610869695606731</v>
+        <v>1.4366362768610586</v>
       </c>
       <c r="H27" s="0">
-        <v>20.311086969560673</v>
+        <v>20.186636276861059</v>
       </c>
       <c r="I27" s="0">
-        <v>1.0610869695606731</v>
+        <v>0.93663627686105855</v>
       </c>
       <c r="J27" s="0">
-        <v>1.0610869695606731</v>
+        <v>0.93663627686105855</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1628,28 +1628,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>679.27729999999997</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.680792223807011</v>
+        <v>21.29237050324776</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.069207776192989456</v>
+        <v>-0.45762949675224007</v>
       </c>
       <c r="G28" s="0">
-        <v>0.069207776192989456</v>
+        <v>0.45762949675224007</v>
       </c>
       <c r="H28" s="0">
-        <v>21.180792223807011</v>
+        <v>20.79237050324776</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.56920777619298946</v>
+        <v>-0.95762949675224007</v>
       </c>
       <c r="J28" s="0">
-        <v>0.56920777619298946</v>
+        <v>0.95762949675224007</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1672,28 +1672,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>527.95719999999994</v>
+        <v>531.55600000000004</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.178379284391266</v>
+        <v>19.32121291139347</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.5716207156087343</v>
+        <v>-1.4287870886065299</v>
       </c>
       <c r="G29" s="0">
-        <v>1.5716207156087343</v>
+        <v>1.4287870886065299</v>
       </c>
       <c r="H29" s="0">
-        <v>18.678379284391266</v>
+        <v>18.82121291139347</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.0716207156087343</v>
+        <v>-1.9287870886065299</v>
       </c>
       <c r="J29" s="0">
-        <v>2.0716207156087343</v>
+        <v>1.9287870886065299</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1716,28 +1716,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>685.61059999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.77672828996986</v>
+        <v>21.746522992707845</v>
       </c>
       <c r="F30" s="0">
-        <v>0.27672828996985999</v>
+        <v>0.24652299270784539</v>
       </c>
       <c r="G30" s="0">
-        <v>0.27672828996985999</v>
+        <v>0.24652299270784539</v>
       </c>
       <c r="H30" s="0">
-        <v>21.27672828996986</v>
+        <v>21.246522992707845</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.22327171003014001</v>
+        <v>-0.25347700729215461</v>
       </c>
       <c r="J30" s="0">
-        <v>0.22327171003014001</v>
+        <v>0.25347700729215461</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>678.49210000000005</v>
+        <v>683.32539999999995</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.643649785755475</v>
+        <v>21.681005330404282</v>
       </c>
       <c r="F31" s="0">
-        <v>2.1436497857554748</v>
+        <v>2.1810053304042825</v>
       </c>
       <c r="G31" s="0">
-        <v>2.1436497857554748</v>
+        <v>2.1810053304042825</v>
       </c>
       <c r="H31" s="0">
-        <v>21.143649785755475</v>
+        <v>21.181005330404282</v>
       </c>
       <c r="I31" s="0">
-        <v>1.6436497857554748</v>
+        <v>1.6810053304042825</v>
       </c>
       <c r="J31" s="0">
-        <v>1.6436497857554748</v>
+        <v>1.6810053304042825</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1804,28 +1804,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>656.11270000000002</v>
+        <v>669.30840000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.083663958407207</v>
+        <v>21.299533197008451</v>
       </c>
       <c r="F32" s="0">
-        <v>1.5836639584072074</v>
+        <v>1.7995331970084507</v>
       </c>
       <c r="G32" s="0">
-        <v>1.5836639584072074</v>
+        <v>1.7995331970084507</v>
       </c>
       <c r="H32" s="0">
-        <v>20.583663958407207</v>
+        <v>20.799533197008451</v>
       </c>
       <c r="I32" s="0">
-        <v>1.0836639584072074</v>
+        <v>1.2995331970084507</v>
       </c>
       <c r="J32" s="0">
-        <v>1.0836639584072074</v>
+        <v>1.2995331970084507</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1848,31 +1848,31 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>679.53120000000001</v>
+        <v>712.56219999999996</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.351933560928245</v>
+        <v>22.151259540367867</v>
       </c>
       <c r="F33" s="0">
-        <v>0.35193356092824502</v>
+        <v>1.1512595403678674</v>
       </c>
       <c r="G33" s="0">
-        <v>0.35193356092824502</v>
+        <v>1.1512595403678674</v>
       </c>
       <c r="H33" s="0">
-        <v>20.851933560928245</v>
+        <v>21.651259540367867</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.14806643907175498</v>
+        <v>0.65125954036786737</v>
       </c>
       <c r="J33" s="0">
-        <v>0.14806643907175498</v>
+        <v>0.65125954036786737</v>
       </c>
       <c r="K33" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="0">
         <v>1</v>
@@ -1892,28 +1892,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>611.39670000000001</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.140756124007709</v>
+        <v>20.095367644267856</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.10924387599229135</v>
+        <v>-0.15463235573214362</v>
       </c>
       <c r="G34" s="0">
-        <v>0.10924387599229135</v>
+        <v>0.15463235573214362</v>
       </c>
       <c r="H34" s="0">
-        <v>19.640756124007709</v>
+        <v>19.595367644267856</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.60924387599229135</v>
+        <v>-0.65463235573214362</v>
       </c>
       <c r="J34" s="0">
-        <v>0.60924387599229135</v>
+        <v>0.65463235573214362</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>622.68050000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.321588739364621</v>
+        <v>20.425428722838831</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.1784112606353787</v>
+        <v>-1.0745712771611693</v>
       </c>
       <c r="G35" s="0">
-        <v>1.1784112606353787</v>
+        <v>1.0745712771611693</v>
       </c>
       <c r="H35" s="0">
-        <v>19.821588739364621</v>
+        <v>19.925428722838831</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.6784112606353787</v>
+        <v>-1.5745712771611693</v>
       </c>
       <c r="J35" s="0">
-        <v>1.6784112606353787</v>
+        <v>1.5745712771611693</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1980,31 +1980,31 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>601.95100000000002</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>19.914206125735543</v>
+        <v>20.016501977641706</v>
       </c>
       <c r="F36" s="0">
-        <v>0.41420612573554294</v>
+        <v>0.51650197764170613</v>
       </c>
       <c r="G36" s="0">
-        <v>0.41420612573554294</v>
+        <v>0.51650197764170613</v>
       </c>
       <c r="H36" s="0">
-        <v>19.414206125735543</v>
+        <v>19.516501977641706</v>
       </c>
       <c r="I36" s="0">
-        <v>-0.08579387426445706</v>
+        <v>0.016501977641706134</v>
       </c>
       <c r="J36" s="0">
-        <v>0.08579387426445706</v>
+        <v>0.016501977641706134</v>
       </c>
       <c r="K36" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="0">
         <v>1</v>
@@ -2024,28 +2024,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>726.80799999999999</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.437699510830932</v>
+        <v>22.462789781250276</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.5623004891690684</v>
+        <v>-2.5372102187497241</v>
       </c>
       <c r="G37" s="0">
-        <v>2.5623004891690684</v>
+        <v>2.5372102187497241</v>
       </c>
       <c r="H37" s="0">
-        <v>21.937699510830932</v>
+        <v>21.962789781250276</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.0623004891690684</v>
+        <v>-3.0372102187497241</v>
       </c>
       <c r="J37" s="0">
-        <v>3.0623004891690684</v>
+        <v>3.0372102187497241</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>599.73789999999997</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.781271446496419</v>
+        <v>19.768081102893305</v>
       </c>
       <c r="F38" s="0">
-        <v>0.78127144649641878</v>
+        <v>0.768081102893305</v>
       </c>
       <c r="G38" s="0">
-        <v>0.78127144649641878</v>
+        <v>0.768081102893305</v>
       </c>
       <c r="H38" s="0">
-        <v>19.281271446496419</v>
+        <v>19.268081102893305</v>
       </c>
       <c r="I38" s="0">
-        <v>0.28127144649641878</v>
+        <v>0.268081102893305</v>
       </c>
       <c r="J38" s="0">
-        <v>0.28127144649641878</v>
+        <v>0.268081102893305</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2112,28 +2112,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>700.04589999999996</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>22.015168081422118</v>
+        <v>22.113155669747396</v>
       </c>
       <c r="F39" s="0">
-        <v>3.015168081422118</v>
+        <v>3.1131556697473961</v>
       </c>
       <c r="G39" s="0">
-        <v>3.015168081422118</v>
+        <v>3.1131556697473961</v>
       </c>
       <c r="H39" s="0">
-        <v>21.515168081422118</v>
+        <v>21.613155669747396</v>
       </c>
       <c r="I39" s="0">
-        <v>2.515168081422118</v>
+        <v>2.6131556697473961</v>
       </c>
       <c r="J39" s="0">
-        <v>2.515168081422118</v>
+        <v>2.6131556697473961</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2156,28 +2156,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>777.77840000000003</v>
+        <v>776.98199999999997</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>24.429591918397694</v>
+        <v>24.714301558676652</v>
       </c>
       <c r="F40" s="0">
-        <v>3.4295919183976942</v>
+        <v>3.7143015586766523</v>
       </c>
       <c r="G40" s="0">
-        <v>3.4295919183976942</v>
+        <v>3.7143015586766523</v>
       </c>
       <c r="H40" s="0">
-        <v>23.929591918397694</v>
+        <v>24.214301558676652</v>
       </c>
       <c r="I40" s="0">
-        <v>2.9295919183976942</v>
+        <v>3.2143015586766523</v>
       </c>
       <c r="J40" s="0">
-        <v>2.9295919183976942</v>
+        <v>3.2143015586766523</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2200,28 +2200,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>673.32410000000004</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.331612219465093</v>
+        <v>21.405122474971378</v>
       </c>
       <c r="F41" s="0">
-        <v>0.83161221946509301</v>
+        <v>0.90512247497137821</v>
       </c>
       <c r="G41" s="0">
-        <v>0.83161221946509301</v>
+        <v>0.90512247497137821</v>
       </c>
       <c r="H41" s="0">
-        <v>20.831612219465093</v>
+        <v>20.905122474971378</v>
       </c>
       <c r="I41" s="0">
-        <v>0.33161221946509301</v>
+        <v>0.40512247497137821</v>
       </c>
       <c r="J41" s="0">
-        <v>0.33161221946509301</v>
+        <v>0.40512247497137821</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2244,28 +2244,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>518.52380000000005</v>
+        <v>526.36469999999997</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.089490199914998</v>
+        <v>19.280698089999582</v>
       </c>
       <c r="F42" s="0">
-        <v>-0.16050980008500204</v>
+        <v>0.030698089999582123</v>
       </c>
       <c r="G42" s="0">
-        <v>0.16050980008500204</v>
+        <v>0.030698089999582123</v>
       </c>
       <c r="H42" s="0">
-        <v>18.589490199914998</v>
+        <v>18.780698089999582</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.66050980008500204</v>
+        <v>-0.46930191000041788</v>
       </c>
       <c r="J42" s="0">
-        <v>0.66050980008500204</v>
+        <v>0.46930191000041788</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2288,28 +2288,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>586.85530000000006</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.657816528089359</v>
+        <v>19.653284439610474</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.34218347191064069</v>
+        <v>-0.34671556038952645</v>
       </c>
       <c r="G43" s="0">
-        <v>0.34218347191064069</v>
+        <v>0.34671556038952645</v>
       </c>
       <c r="H43" s="0">
-        <v>19.157816528089359</v>
+        <v>19.153284439610474</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.84218347191064069</v>
+        <v>-0.84671556038952644</v>
       </c>
       <c r="J43" s="0">
-        <v>0.84218347191064069</v>
+        <v>0.84671556038952644</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2332,28 +2332,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>663.21749999999997</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.160066819301957</v>
+        <v>21.228512240278569</v>
       </c>
       <c r="F44" s="0">
-        <v>1.1600668193019565</v>
+        <v>1.2285122402785689</v>
       </c>
       <c r="G44" s="0">
-        <v>1.1600668193019565</v>
+        <v>1.2285122402785689</v>
       </c>
       <c r="H44" s="0">
-        <v>20.660066819301957</v>
+        <v>20.728512240278569</v>
       </c>
       <c r="I44" s="0">
-        <v>0.66006681930195654</v>
+        <v>0.72851224027856887</v>
       </c>
       <c r="J44" s="0">
-        <v>0.66006681930195654</v>
+        <v>0.72851224027856887</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2376,28 +2376,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>582.90459999999996</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.862197661277765</v>
+        <v>19.573358861773311</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.13780233872223491</v>
+        <v>-0.42664113822668881</v>
       </c>
       <c r="G45" s="0">
-        <v>0.13780233872223491</v>
+        <v>0.42664113822668881</v>
       </c>
       <c r="H45" s="0">
-        <v>19.362197661277765</v>
+        <v>19.073358861773311</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.63780233872223491</v>
+        <v>-0.92664113822668881</v>
       </c>
       <c r="J45" s="0">
-        <v>0.63780233872223491</v>
+        <v>0.92664113822668881</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2420,28 +2420,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>728.66980000000001</v>
+        <v>732.64890000000003</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>22.830284680599608</v>
+        <v>22.872264714902272</v>
       </c>
       <c r="F46" s="0">
-        <v>0.83028468059960758</v>
+        <v>0.87226471490227198</v>
       </c>
       <c r="G46" s="0">
-        <v>0.83028468059960758</v>
+        <v>0.87226471490227198</v>
       </c>
       <c r="H46" s="0">
-        <v>22.330284680599608</v>
+        <v>22.372264714902272</v>
       </c>
       <c r="I46" s="0">
-        <v>0.33028468059960758</v>
+        <v>0.37226471490227198</v>
       </c>
       <c r="J46" s="0">
-        <v>0.33028468059960758</v>
+        <v>0.37226471490227198</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>1</v>
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>697.34799999999996</v>
+        <v>704.21619999999996</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>22.122399134833191</v>
+        <v>22.212955580169456</v>
       </c>
       <c r="F47" s="0">
-        <v>0.12239913483319143</v>
+        <v>0.21295558016945648</v>
       </c>
       <c r="G47" s="0">
-        <v>0.12239913483319143</v>
+        <v>0.21295558016945648</v>
       </c>
       <c r="H47" s="0">
-        <v>21.622399134833191</v>
+        <v>21.712955580169456</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.37760086516680858</v>
+        <v>-0.28704441983054352</v>
       </c>
       <c r="J47" s="0">
-        <v>0.37760086516680858</v>
+        <v>0.28704441983054352</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2508,28 +2508,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>696.77610000000004</v>
+        <v>707.67989999999998</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.736700244175989</v>
+        <v>21.868145283351971</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.2632997558240113</v>
+        <v>-1.1318547166480286</v>
       </c>
       <c r="G48" s="0">
-        <v>1.2632997558240113</v>
+        <v>1.1318547166480286</v>
       </c>
       <c r="H48" s="0">
-        <v>21.236700244175989</v>
+        <v>21.368145283351971</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.7632997558240113</v>
+        <v>-1.6318547166480286</v>
       </c>
       <c r="J48" s="0">
-        <v>1.7632997558240113</v>
+        <v>1.6318547166480286</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2552,28 +2552,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>664.47260000000006</v>
+        <v>666.81700000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.038226964237374</v>
+        <v>20.831053281467717</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.71177303576262574</v>
+        <v>-0.9189467185322826</v>
       </c>
       <c r="G49" s="0">
-        <v>0.71177303576262574</v>
+        <v>0.9189467185322826</v>
       </c>
       <c r="H49" s="0">
-        <v>20.538226964237374</v>
+        <v>20.331053281467717</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.2117730357626257</v>
+        <v>-1.4189467185322826</v>
       </c>
       <c r="J49" s="0">
-        <v>1.2117730357626257</v>
+        <v>1.4189467185322826</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2596,28 +2596,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>686.67639999999995</v>
+        <v>688.77390000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.738379379786814</v>
+        <v>21.551145842457235</v>
       </c>
       <c r="F50" s="0">
-        <v>0.23837937978681367</v>
+        <v>0.051145842457234636</v>
       </c>
       <c r="G50" s="0">
-        <v>0.23837937978681367</v>
+        <v>0.051145842457234636</v>
       </c>
       <c r="H50" s="0">
-        <v>21.238379379786814</v>
+        <v>21.051145842457235</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.26162062021318633</v>
+        <v>-0.44885415754276537</v>
       </c>
       <c r="J50" s="0">
-        <v>0.26162062021318633</v>
+        <v>0.44885415754276537</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2640,28 +2640,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>616.17359999999997</v>
+        <v>615.82560000000001</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.27429724804151</v>
+        <v>20.190776622533747</v>
       </c>
       <c r="F51" s="0">
-        <v>1.0742972480415105</v>
+        <v>0.99077662253374754</v>
       </c>
       <c r="G51" s="0">
-        <v>1.0742972480415105</v>
+        <v>0.99077662253374754</v>
       </c>
       <c r="H51" s="0">
-        <v>19.77429724804151</v>
+        <v>19.690776622533747</v>
       </c>
       <c r="I51" s="0">
-        <v>0.5742972480415105</v>
+        <v>0.49077662253374754</v>
       </c>
       <c r="J51" s="0">
-        <v>0.5742972480415105</v>
+        <v>0.49077662253374754</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2684,28 +2684,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>575.9733</v>
+        <v>568.91740000000004</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.781121494833339</v>
+        <v>19.451856118416636</v>
       </c>
       <c r="F52" s="0">
-        <v>2.2811214948333394</v>
+        <v>1.9518561184166359</v>
       </c>
       <c r="G52" s="0">
-        <v>2.2811214948333394</v>
+        <v>1.9518561184166359</v>
       </c>
       <c r="H52" s="0">
-        <v>19.281121494833339</v>
+        <v>18.951856118416636</v>
       </c>
       <c r="I52" s="0">
-        <v>1.7811214948333394</v>
+        <v>1.4518561184166359</v>
       </c>
       <c r="J52" s="0">
-        <v>1.7811214948333394</v>
+        <v>1.4518561184166359</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2728,28 +2728,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>589.5335</v>
+        <v>594.03499999999997</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.935941789933629</v>
+        <v>19.952856754467639</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5359417899336307</v>
+        <v>1.5528567544676406</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5359417899336307</v>
+        <v>1.5528567544676406</v>
       </c>
       <c r="H53" s="0">
-        <v>19.435941789933629</v>
+        <v>19.452856754467639</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0359417899336307</v>
+        <v>1.0528567544676406</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0359417899336307</v>
+        <v>1.0528567544676406</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2772,28 +2772,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>563.72389999999996</v>
+        <v>566.51940000000002</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.629052591857619</v>
+        <v>19.534708614094726</v>
       </c>
       <c r="F54" s="0">
-        <v>0.62905259185761864</v>
+        <v>0.53470861409472548</v>
       </c>
       <c r="G54" s="0">
-        <v>0.62905259185761864</v>
+        <v>0.53470861409472548</v>
       </c>
       <c r="H54" s="0">
-        <v>19.129052591857619</v>
+        <v>19.034708614094726</v>
       </c>
       <c r="I54" s="0">
-        <v>0.12905259185761864</v>
+        <v>0.034708614094725476</v>
       </c>
       <c r="J54" s="0">
-        <v>0.12905259185761864</v>
+        <v>0.034708614094725476</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2816,28 +2816,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>614.26739999999995</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>19.785163322273878</v>
+        <v>19.940101280553549</v>
       </c>
       <c r="F55" s="0">
-        <v>0.28516332227387764</v>
+        <v>0.44010128055354869</v>
       </c>
       <c r="G55" s="0">
-        <v>0.28516332227387764</v>
+        <v>0.44010128055354869</v>
       </c>
       <c r="H55" s="0">
-        <v>19.285163322273878</v>
+        <v>19.440101280553549</v>
       </c>
       <c r="I55" s="0">
-        <v>-0.21483667772612236</v>
+        <v>-0.05989871944645131</v>
       </c>
       <c r="J55" s="0">
-        <v>0.21483667772612236</v>
+        <v>0.05989871944645131</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>0</v>
@@ -2860,28 +2860,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>717.47789999999998</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>22.81397019808886</v>
+        <v>22.526024925778771</v>
       </c>
       <c r="F56" s="0">
-        <v>2.3139701980888603</v>
+        <v>2.0260249257787706</v>
       </c>
       <c r="G56" s="0">
-        <v>2.3139701980888603</v>
+        <v>2.0260249257787706</v>
       </c>
       <c r="H56" s="0">
-        <v>22.31397019808886</v>
+        <v>22.026024925778771</v>
       </c>
       <c r="I56" s="0">
-        <v>1.8139701980888603</v>
+        <v>1.5260249257787706</v>
       </c>
       <c r="J56" s="0">
-        <v>1.8139701980888603</v>
+        <v>1.5260249257787706</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2904,28 +2904,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>656.12369999999999</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.690467325788994</v>
+        <v>20.745218702182413</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.30953267421100605</v>
+        <v>-0.25478129781758696</v>
       </c>
       <c r="G57" s="0">
-        <v>0.30953267421100605</v>
+        <v>0.25478129781758696</v>
       </c>
       <c r="H57" s="0">
-        <v>20.190467325788994</v>
+        <v>20.245218702182413</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.80953267421100605</v>
+        <v>-0.75478129781758696</v>
       </c>
       <c r="J57" s="0">
-        <v>0.80953267421100605</v>
+        <v>0.75478129781758696</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>730.19860000000006</v>
+        <v>713.17060000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>22.536161690683485</v>
+        <v>22.146789715511915</v>
       </c>
       <c r="F58" s="0">
-        <v>-0.9638383093165146</v>
+        <v>-1.3532102844880853</v>
       </c>
       <c r="G58" s="0">
-        <v>0.9638383093165146</v>
+        <v>1.3532102844880853</v>
       </c>
       <c r="H58" s="0">
-        <v>22.036161690683485</v>
+        <v>21.646789715511915</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.4638383093165146</v>
+        <v>-1.8532102844880853</v>
       </c>
       <c r="J58" s="0">
-        <v>1.4638383093165146</v>
+        <v>1.8532102844880853</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2992,28 +2992,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>675.12120000000004</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.316914204002714</v>
+        <v>21.453354647770933</v>
       </c>
       <c r="F59" s="0">
-        <v>0.81691420400271397</v>
+        <v>0.95335464777093293</v>
       </c>
       <c r="G59" s="0">
-        <v>0.81691420400271397</v>
+        <v>0.95335464777093293</v>
       </c>
       <c r="H59" s="0">
-        <v>20.816914204002714</v>
+        <v>20.953354647770933</v>
       </c>
       <c r="I59" s="0">
-        <v>0.31691420400271397</v>
+        <v>0.45335464777093293</v>
       </c>
       <c r="J59" s="0">
-        <v>0.31691420400271397</v>
+        <v>0.45335464777093293</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3036,28 +3036,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>689.68129999999997</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.993692350567457</v>
+        <v>21.576230421697272</v>
       </c>
       <c r="F60" s="0">
-        <v>0.49369235056745708</v>
+        <v>0.076230421697271566</v>
       </c>
       <c r="G60" s="0">
-        <v>0.49369235056745708</v>
+        <v>0.076230421697271566</v>
       </c>
       <c r="H60" s="0">
-        <v>21.493692350567457</v>
+        <v>21.076230421697272</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.0063076494325429167</v>
+        <v>-0.42376957830272843</v>
       </c>
       <c r="J60" s="0">
-        <v>0.0063076494325429167</v>
+        <v>0.42376957830272843</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>646.9873</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.77380643589947</v>
+        <v>20.756243671378353</v>
       </c>
       <c r="F61" s="0">
-        <v>0.77380643589946985</v>
+        <v>0.75624367137835336</v>
       </c>
       <c r="G61" s="0">
-        <v>0.77380643589946985</v>
+        <v>0.75624367137835336</v>
       </c>
       <c r="H61" s="0">
-        <v>20.27380643589947</v>
+        <v>20.256243671378353</v>
       </c>
       <c r="I61" s="0">
-        <v>0.27380643589946985</v>
+        <v>0.25624367137835335</v>
       </c>
       <c r="J61" s="0">
-        <v>0.27380643589946985</v>
+        <v>0.25624367137835335</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3124,28 +3124,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>680.14350000000002</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.940131007336959</v>
+        <v>21.408636055750218</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.0598689926630414</v>
+        <v>-1.5913639442497818</v>
       </c>
       <c r="G62" s="0">
-        <v>1.0598689926630414</v>
+        <v>1.5913639442497818</v>
       </c>
       <c r="H62" s="0">
-        <v>21.440131007336959</v>
+        <v>20.908636055750218</v>
       </c>
       <c r="I62" s="0">
-        <v>-1.5598689926630414</v>
+        <v>-2.0913639442497818</v>
       </c>
       <c r="J62" s="0">
-        <v>1.5598689926630414</v>
+        <v>2.0913639442497818</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3168,28 +3168,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>675.0444</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.789620950270951</v>
+        <v>21.510595887035915</v>
       </c>
       <c r="F63" s="0">
-        <v>0.28962095027095103</v>
+        <v>0.010595887035915297</v>
       </c>
       <c r="G63" s="0">
-        <v>0.28962095027095103</v>
+        <v>0.010595887035915297</v>
       </c>
       <c r="H63" s="0">
-        <v>21.289620950270951</v>
+        <v>21.010595887035915</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.21037904972904897</v>
+        <v>-0.4894041129640847</v>
       </c>
       <c r="J63" s="0">
-        <v>0.21037904972904897</v>
+        <v>0.4894041129640847</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3212,28 +3212,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>635.10969999999998</v>
+        <v>638.85119999999995</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.337221113942817</v>
+        <v>20.343204667934987</v>
       </c>
       <c r="F64" s="0">
-        <v>-2.1627788860571826</v>
+        <v>-2.1567953320650126</v>
       </c>
       <c r="G64" s="0">
-        <v>2.1627788860571826</v>
+        <v>2.1567953320650126</v>
       </c>
       <c r="H64" s="0">
-        <v>19.837221113942817</v>
+        <v>19.843204667934987</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.6627788860571826</v>
+        <v>-2.6567953320650126</v>
       </c>
       <c r="J64" s="0">
-        <v>2.6627788860571826</v>
+        <v>2.6567953320650126</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3256,28 +3256,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>595.31380000000001</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>19.947083126811044</v>
+        <v>19.902752520007834</v>
       </c>
       <c r="F65" s="0">
-        <v>0.69708312681104445</v>
+        <v>0.65275252000783368</v>
       </c>
       <c r="G65" s="0">
-        <v>0.69708312681104445</v>
+        <v>0.65275252000783368</v>
       </c>
       <c r="H65" s="0">
-        <v>19.447083126811044</v>
+        <v>19.402752520007834</v>
       </c>
       <c r="I65" s="0">
-        <v>0.19708312681104445</v>
+        <v>0.15275252000783368</v>
       </c>
       <c r="J65" s="0">
-        <v>0.19708312681104445</v>
+        <v>0.15275252000783368</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3300,28 +3300,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>698.0498</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.211227565120908</v>
+        <v>21.437466294229477</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.2887724348790925</v>
+        <v>-2.0625337057705231</v>
       </c>
       <c r="G66" s="0">
-        <v>2.2887724348790925</v>
+        <v>2.0625337057705231</v>
       </c>
       <c r="H66" s="0">
-        <v>20.711227565120908</v>
+        <v>20.937466294229477</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.7887724348790925</v>
+        <v>-2.5625337057705231</v>
       </c>
       <c r="J66" s="0">
-        <v>2.7887724348790925</v>
+        <v>2.5625337057705231</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3344,28 +3344,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>634.08339999999998</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.542192915543211</v>
+        <v>20.56665683524735</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.95780708445678897</v>
+        <v>-0.93334316475264956</v>
       </c>
       <c r="G67" s="0">
-        <v>0.95780708445678897</v>
+        <v>0.93334316475264956</v>
       </c>
       <c r="H67" s="0">
-        <v>20.042192915543211</v>
+        <v>20.06665683524735</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.457807084456789</v>
+        <v>-1.4333431647526496</v>
       </c>
       <c r="J67" s="0">
-        <v>1.457807084456789</v>
+        <v>1.4333431647526496</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>572.66319999999996</v>
+        <v>578.7296</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.752931513098765</v>
+        <v>19.506726354918918</v>
       </c>
       <c r="F68" s="0">
-        <v>0.75293151309876549</v>
+        <v>0.50672635491891782</v>
       </c>
       <c r="G68" s="0">
-        <v>0.75293151309876549</v>
+        <v>0.50672635491891782</v>
       </c>
       <c r="H68" s="0">
-        <v>19.252931513098765</v>
+        <v>19.006726354918918</v>
       </c>
       <c r="I68" s="0">
-        <v>0.25293151309876549</v>
+        <v>0.0067263549189178207</v>
       </c>
       <c r="J68" s="0">
-        <v>0.25293151309876549</v>
+        <v>0.0067263549189178207</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3470,16 +3470,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.115</v>
+        <v>1.127</v>
       </c>
       <c r="C2" s="0">
-        <v>1.407</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>0.38200000000000001</v>
+        <v>0.378</v>
       </c>
       <c r="E2" s="0">
-        <v>0.024</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3489,22 +3489,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0089999999999999993</v>
+        <v>0.023</v>
       </c>
       <c r="C3" s="0">
-        <v>0.014</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.010999999999999999</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0.012999999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G3" s="0">
-        <v>0.80000000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3523,18 +3523,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.143</v>
+        <v>1.171</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.47599999999999998</v>
+        <v>-0.48199999999999999</v>
       </c>
       <c r="F5" s="0">
-        <v>53.700000000000003</v>
+        <v>53.399999999999999</v>
       </c>
       <c r="G5" s="0">
-        <v>39.600000000000001</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="6">
@@ -3542,13 +3542,13 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.0940000000000001</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>1.3919999999999999</v>
+        <v>1.4039999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>0.39200000000000002</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="E6" s="0">
         <v>0.02</v>
@@ -3561,7 +3561,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.131</v>
+        <v>1.167</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -3572,7 +3572,7 @@
         <v>53.700000000000003</v>
       </c>
       <c r="G7" s="0">
-        <v>37.299999999999997</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3680,13 +3680,13 @@
         <v>111</v>
       </c>
       <c r="B2" s="0">
-        <v>9.1541999999999995</v>
+        <v>9.0012000000000008</v>
       </c>
       <c r="C2" s="0">
-        <v>1.6413</v>
+        <v>1.6853</v>
       </c>
       <c r="D2" s="0">
-        <v>5.577</v>
+        <v>5.3410000000000002</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3697,13 +3697,13 @@
         <v>112</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0183</v>
+        <v>0.018499999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025000000000000001</v>
+        <v>0.0025999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>7.2450000000000001</v>
+        <v>7.1459999999999999</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>

--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化.xlsx
@@ -484,28 +484,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>606.4973</v>
+        <v>610.42669999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>19.842236501118745</v>
+        <v>19.811310064583243</v>
       </c>
       <c r="F2" s="0">
-        <v>-3.1577634988812555</v>
+        <v>-3.1886899354167575</v>
       </c>
       <c r="G2" s="0">
-        <v>3.1577634988812555</v>
+        <v>3.1886899354167575</v>
       </c>
       <c r="H2" s="0">
-        <v>19.342236501118745</v>
+        <v>19.311310064583243</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.6577634988812555</v>
+        <v>-3.6886899354167575</v>
       </c>
       <c r="J2" s="0">
-        <v>3.6577634988812555</v>
+        <v>3.6886899354167575</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -528,28 +528,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>609.20730000000003</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.090406914195555</v>
+        <v>20.169890279747865</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.90959308580444542</v>
+        <v>-0.83010972025213547</v>
       </c>
       <c r="G3" s="0">
-        <v>0.90959308580444542</v>
+        <v>0.83010972025213547</v>
       </c>
       <c r="H3" s="0">
-        <v>19.590406914195555</v>
+        <v>19.669890279747865</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.4095930858044454</v>
+        <v>-1.3301097202521355</v>
       </c>
       <c r="J3" s="0">
-        <v>1.4095930858044454</v>
+        <v>1.3301097202521355</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -572,28 +572,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>755.06500000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.107745147697024</v>
+        <v>23.246304318645024</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.39225485230297608</v>
+        <v>-0.25369568135497644</v>
       </c>
       <c r="G4" s="0">
-        <v>0.39225485230297608</v>
+        <v>0.25369568135497644</v>
       </c>
       <c r="H4" s="0">
-        <v>22.607745147697024</v>
+        <v>22.746304318645024</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.89225485230297608</v>
+        <v>-0.75369568135497644</v>
       </c>
       <c r="J4" s="0">
-        <v>0.89225485230297608</v>
+        <v>0.75369568135497644</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -616,28 +616,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.86080000000004</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.604443642841563</v>
+        <v>19.628235466402099</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.3955563571584371</v>
+        <v>-1.3717645335979007</v>
       </c>
       <c r="G5" s="0">
-        <v>1.3955563571584371</v>
+        <v>1.3717645335979007</v>
       </c>
       <c r="H5" s="0">
-        <v>19.104443642841563</v>
+        <v>19.128235466402099</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.8955563571584371</v>
+        <v>-1.8717645335979007</v>
       </c>
       <c r="J5" s="0">
-        <v>1.8955563571584371</v>
+        <v>1.8717645335979007</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -660,28 +660,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>634.26990000000001</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.511320650915728</v>
+        <v>20.398898630456081</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.98867934908427202</v>
+        <v>-1.1011013695439189</v>
       </c>
       <c r="G6" s="0">
-        <v>0.98867934908427202</v>
+        <v>1.1011013695439189</v>
       </c>
       <c r="H6" s="0">
-        <v>20.011320650915728</v>
+        <v>19.898898630456081</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.488679349084272</v>
+        <v>-1.6011013695439189</v>
       </c>
       <c r="J6" s="0">
-        <v>1.488679349084272</v>
+        <v>1.6011013695439189</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -704,28 +704,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>691.86599999999999</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.636806640470915</v>
+        <v>22.279770034521512</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.3631933595290846</v>
+        <v>0.27977003452151195</v>
       </c>
       <c r="G7" s="0">
-        <v>0.3631933595290846</v>
+        <v>0.27977003452151195</v>
       </c>
       <c r="H7" s="0">
-        <v>21.136806640470915</v>
+        <v>21.779770034521512</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.8631933595290846</v>
+        <v>-0.22022996547848806</v>
       </c>
       <c r="J7" s="0">
-        <v>0.8631933595290846</v>
+        <v>0.22022996547848806</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -748,28 +748,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>763.82230000000004</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.573508183523323</v>
+        <v>23.851740851255773</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.4264918164766769</v>
+        <v>-1.1482591487442271</v>
       </c>
       <c r="G8" s="0">
-        <v>1.4264918164766769</v>
+        <v>1.1482591487442271</v>
       </c>
       <c r="H8" s="0">
-        <v>23.073508183523323</v>
+        <v>23.351740851255773</v>
       </c>
       <c r="I8" s="0">
-        <v>-1.9264918164766769</v>
+        <v>-1.6482591487442271</v>
       </c>
       <c r="J8" s="0">
-        <v>1.9264918164766769</v>
+        <v>1.6482591487442271</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -792,28 +792,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>612.55169999999998</v>
+        <v>584.5915</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.140202468328937</v>
+        <v>19.771966263909132</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.3597975316710631</v>
+        <v>-0.72803373609086819</v>
       </c>
       <c r="G9" s="0">
-        <v>0.3597975316710631</v>
+        <v>0.72803373609086819</v>
       </c>
       <c r="H9" s="0">
-        <v>19.640202468328937</v>
+        <v>19.271966263909132</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.8597975316710631</v>
+        <v>-1.2280337360908682</v>
       </c>
       <c r="J9" s="0">
-        <v>0.8597975316710631</v>
+        <v>1.2280337360908682</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -836,28 +836,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>647.83249999999998</v>
+        <v>648.39279999999997</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>20.787880293704873</v>
+        <v>20.692282209268896</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.21211970629512678</v>
+        <v>-0.30771779073110395</v>
       </c>
       <c r="G10" s="0">
-        <v>0.21211970629512678</v>
+        <v>0.30771779073110395</v>
       </c>
       <c r="H10" s="0">
-        <v>20.287880293704873</v>
+        <v>20.192282209268896</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.71211970629512678</v>
+        <v>-0.80771779073110395</v>
       </c>
       <c r="J10" s="0">
-        <v>0.71211970629512678</v>
+        <v>0.80771779073110395</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -880,28 +880,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>468.75369999999998</v>
+        <v>466.6764</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.586004925704792</v>
+        <v>19.937209597451748</v>
       </c>
       <c r="F11" s="0">
-        <v>1.5860049257047919</v>
+        <v>1.9372095974517478</v>
       </c>
       <c r="G11" s="0">
-        <v>1.5860049257047919</v>
+        <v>1.9372095974517478</v>
       </c>
       <c r="H11" s="0">
-        <v>19.086004925704792</v>
+        <v>19.437209597451748</v>
       </c>
       <c r="I11" s="0">
-        <v>1.0860049257047919</v>
+        <v>1.4372095974517478</v>
       </c>
       <c r="J11" s="0">
-        <v>1.0860049257047919</v>
+        <v>1.4372095974517478</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -924,28 +924,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>745.02800000000002</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>23.14196628846112</v>
+        <v>23.367897297075629</v>
       </c>
       <c r="F12" s="0">
-        <v>-1.8580337115388801</v>
+        <v>-1.6321027029243709</v>
       </c>
       <c r="G12" s="0">
-        <v>1.8580337115388801</v>
+        <v>1.6321027029243709</v>
       </c>
       <c r="H12" s="0">
-        <v>22.64196628846112</v>
+        <v>22.867897297075629</v>
       </c>
       <c r="I12" s="0">
-        <v>-2.3580337115388801</v>
+        <v>-2.1321027029243709</v>
       </c>
       <c r="J12" s="0">
-        <v>2.3580337115388801</v>
+        <v>2.1321027029243709</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -968,28 +968,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>674.10310000000004</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.487994294786844</v>
+        <v>21.025673895349097</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.0120057052131557</v>
+        <v>-1.4743261046509026</v>
       </c>
       <c r="G13" s="0">
-        <v>1.0120057052131557</v>
+        <v>1.4743261046509026</v>
       </c>
       <c r="H13" s="0">
-        <v>20.987994294786844</v>
+        <v>20.525673895349097</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.5120057052131557</v>
+        <v>-1.9743261046509026</v>
       </c>
       <c r="J13" s="0">
-        <v>1.5120057052131557</v>
+        <v>1.9743261046509026</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1012,28 +1012,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>678.64329999999995</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.376831548872094</v>
+        <v>21.525466052432464</v>
       </c>
       <c r="F14" s="0">
-        <v>0.87683154887209369</v>
+        <v>1.0254660524324635</v>
       </c>
       <c r="G14" s="0">
-        <v>0.87683154887209369</v>
+        <v>1.0254660524324635</v>
       </c>
       <c r="H14" s="0">
-        <v>20.876831548872094</v>
+        <v>21.025466052432464</v>
       </c>
       <c r="I14" s="0">
-        <v>0.37683154887209369</v>
+        <v>0.52546605243246347</v>
       </c>
       <c r="J14" s="0">
-        <v>0.37683154887209369</v>
+        <v>0.52546605243246347</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1056,28 +1056,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>588.29200000000003</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>19.673175069373656</v>
+        <v>19.727925167909863</v>
       </c>
       <c r="F15" s="0">
-        <v>0.17317506937365579</v>
+        <v>0.22792516790986284</v>
       </c>
       <c r="G15" s="0">
-        <v>0.17317506937365579</v>
+        <v>0.22792516790986284</v>
       </c>
       <c r="H15" s="0">
-        <v>19.173175069373656</v>
+        <v>19.227925167909863</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.32682493062634421</v>
+        <v>-0.27207483209013716</v>
       </c>
       <c r="J15" s="0">
-        <v>0.32682493062634421</v>
+        <v>0.27207483209013716</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>0</v>
@@ -1100,28 +1100,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.86260000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>20.239344029463112</v>
+        <v>20.26027808340892</v>
       </c>
       <c r="F16" s="0">
-        <v>0.73934402946311195</v>
+        <v>0.76027808340892022</v>
       </c>
       <c r="G16" s="0">
-        <v>0.73934402946311195</v>
+        <v>0.76027808340892022</v>
       </c>
       <c r="H16" s="0">
-        <v>19.739344029463112</v>
+        <v>19.76027808340892</v>
       </c>
       <c r="I16" s="0">
-        <v>0.23934402946311195</v>
+        <v>0.26027808340892022</v>
       </c>
       <c r="J16" s="0">
-        <v>0.23934402946311195</v>
+        <v>0.26027808340892022</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1144,28 +1144,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>557.87480000000005</v>
+        <v>564.40920000000006</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.552710564108011</v>
+        <v>19.54899489717241</v>
       </c>
       <c r="F17" s="0">
-        <v>1.0527105641080112</v>
+        <v>1.0489948971724097</v>
       </c>
       <c r="G17" s="0">
-        <v>1.0527105641080112</v>
+        <v>1.0489948971724097</v>
       </c>
       <c r="H17" s="0">
-        <v>19.052710564108011</v>
+        <v>19.04899489717241</v>
       </c>
       <c r="I17" s="0">
-        <v>0.55271056410801123</v>
+        <v>0.54899489717240968</v>
       </c>
       <c r="J17" s="0">
-        <v>0.55271056410801123</v>
+        <v>0.54899489717240968</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1188,28 +1188,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>734.02059999999995</v>
+        <v>736.66660000000002</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>22.90277258058093</v>
+        <v>23.058903648884012</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.84722741941907032</v>
+        <v>-0.69109635111598777</v>
       </c>
       <c r="G18" s="0">
-        <v>0.84722741941907032</v>
+        <v>0.69109635111598777</v>
       </c>
       <c r="H18" s="0">
-        <v>22.40277258058093</v>
+        <v>22.558903648884012</v>
       </c>
       <c r="I18" s="0">
-        <v>-1.3472274194190703</v>
+        <v>-1.1910963511159878</v>
       </c>
       <c r="J18" s="0">
-        <v>1.3472274194190703</v>
+        <v>1.1910963511159878</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1232,28 +1232,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>674.8356</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.916699364719882</v>
+        <v>21.134172034787103</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.3333006352801178</v>
+        <v>-1.1158279652128975</v>
       </c>
       <c r="G19" s="0">
-        <v>1.3333006352801178</v>
+        <v>1.1158279652128975</v>
       </c>
       <c r="H19" s="0">
-        <v>20.416699364719882</v>
+        <v>20.634172034787103</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.8333006352801178</v>
+        <v>-1.6158279652128975</v>
       </c>
       <c r="J19" s="0">
-        <v>1.8333006352801178</v>
+        <v>1.6158279652128975</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1276,28 +1276,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>758.93589999999995</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.347195010719474</v>
+        <v>23.554634926218782</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.1528049892805257</v>
+        <v>-1.9453650737812183</v>
       </c>
       <c r="G20" s="0">
-        <v>2.1528049892805257</v>
+        <v>1.9453650737812183</v>
       </c>
       <c r="H20" s="0">
-        <v>22.847195010719474</v>
+        <v>23.054634926218782</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.6528049892805257</v>
+        <v>-2.4453650737812183</v>
       </c>
       <c r="J20" s="0">
-        <v>2.6528049892805257</v>
+        <v>2.4453650737812183</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1320,28 +1320,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>530.03160000000003</v>
+        <v>533.39049999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>18.876228640577274</v>
+        <v>19.079846070791049</v>
       </c>
       <c r="F21" s="0">
-        <v>-3.6237713594227259</v>
+        <v>-3.4201539292089507</v>
       </c>
       <c r="G21" s="0">
-        <v>3.6237713594227259</v>
+        <v>3.4201539292089507</v>
       </c>
       <c r="H21" s="0">
-        <v>18.376228640577274</v>
+        <v>18.579846070791049</v>
       </c>
       <c r="I21" s="0">
-        <v>-4.1237713594227259</v>
+        <v>-3.9201539292089507</v>
       </c>
       <c r="J21" s="0">
-        <v>4.1237713594227259</v>
+        <v>3.9201539292089507</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1364,28 +1364,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>619.3691</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.301415660704343</v>
+        <v>20.255639734866339</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.1985843392956568</v>
+        <v>-1.2443602651336612</v>
       </c>
       <c r="G22" s="0">
-        <v>1.1985843392956568</v>
+        <v>1.2443602651336612</v>
       </c>
       <c r="H22" s="0">
-        <v>19.801415660704343</v>
+        <v>19.755639734866339</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.6985843392956568</v>
+        <v>-1.7443602651336612</v>
       </c>
       <c r="J22" s="0">
-        <v>1.6985843392956568</v>
+        <v>1.7443602651336612</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1408,28 +1408,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>681.04340000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.427805265640963</v>
+        <v>21.233486511666182</v>
       </c>
       <c r="F23" s="0">
-        <v>1.4278052656409628</v>
+        <v>1.2334865116661824</v>
       </c>
       <c r="G23" s="0">
-        <v>1.4278052656409628</v>
+        <v>1.2334865116661824</v>
       </c>
       <c r="H23" s="0">
-        <v>20.927805265640963</v>
+        <v>20.733486511666182</v>
       </c>
       <c r="I23" s="0">
-        <v>0.92780526564096277</v>
+        <v>0.7334865116661824</v>
       </c>
       <c r="J23" s="0">
-        <v>0.92780526564096277</v>
+        <v>0.7334865116661824</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1452,28 +1452,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>585.4384</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.786843584350411</v>
+        <v>19.766942052861271</v>
       </c>
       <c r="F24" s="0">
-        <v>0.28684358435041091</v>
+        <v>0.26694205286127115</v>
       </c>
       <c r="G24" s="0">
-        <v>0.28684358435041091</v>
+        <v>0.26694205286127115</v>
       </c>
       <c r="H24" s="0">
-        <v>19.286843584350411</v>
+        <v>19.266942052861271</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.21315641564958909</v>
+        <v>-0.23305794713872885</v>
       </c>
       <c r="J24" s="0">
-        <v>0.21315641564958909</v>
+        <v>0.23305794713872885</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1496,28 +1496,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>581.173</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.543219559556985</v>
+        <v>19.84045531979994</v>
       </c>
       <c r="F25" s="0">
-        <v>1.0432195595569844</v>
+        <v>1.3404553197999398</v>
       </c>
       <c r="G25" s="0">
-        <v>1.0432195595569844</v>
+        <v>1.3404553197999398</v>
       </c>
       <c r="H25" s="0">
-        <v>19.043219559556985</v>
+        <v>19.34045531979994</v>
       </c>
       <c r="I25" s="0">
-        <v>0.54321955955698442</v>
+        <v>0.84045531979993982</v>
       </c>
       <c r="J25" s="0">
-        <v>0.54321955955698442</v>
+        <v>0.84045531979993982</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1540,28 +1540,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>692.99239999999998</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>21.94346003127864</v>
+        <v>21.882533474650465</v>
       </c>
       <c r="F26" s="0">
-        <v>0.69346003127864009</v>
+        <v>0.63253347465046517</v>
       </c>
       <c r="G26" s="0">
-        <v>0.69346003127864009</v>
+        <v>0.63253347465046517</v>
       </c>
       <c r="H26" s="0">
-        <v>21.44346003127864</v>
+        <v>21.382533474650465</v>
       </c>
       <c r="I26" s="0">
-        <v>0.19346003127864009</v>
+        <v>0.13253347465046517</v>
       </c>
       <c r="J26" s="0">
-        <v>0.19346003127864009</v>
+        <v>0.13253347465046517</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1584,28 +1584,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>643.06439999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.686636276861059</v>
+        <v>20.756847316770507</v>
       </c>
       <c r="F27" s="0">
-        <v>1.4366362768610586</v>
+        <v>1.5068473167705072</v>
       </c>
       <c r="G27" s="0">
-        <v>1.4366362768610586</v>
+        <v>1.5068473167705072</v>
       </c>
       <c r="H27" s="0">
-        <v>20.186636276861059</v>
+        <v>20.256847316770507</v>
       </c>
       <c r="I27" s="0">
-        <v>0.93663627686105855</v>
+        <v>1.0068473167705072</v>
       </c>
       <c r="J27" s="0">
-        <v>0.93663627686105855</v>
+        <v>1.0068473167705072</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1628,28 +1628,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>679.27729999999997</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.29237050324776</v>
+        <v>22.033254719634204</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.45762949675224007</v>
+        <v>0.28325471963420412</v>
       </c>
       <c r="G28" s="0">
-        <v>0.45762949675224007</v>
+        <v>0.28325471963420412</v>
       </c>
       <c r="H28" s="0">
-        <v>20.79237050324776</v>
+        <v>21.533254719634204</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.95762949675224007</v>
+        <v>-0.21674528036579588</v>
       </c>
       <c r="J28" s="0">
-        <v>0.95762949675224007</v>
+        <v>0.21674528036579588</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1672,28 +1672,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>531.55600000000004</v>
+        <v>527.93060000000003</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.32121291139347</v>
+        <v>19.206828557347198</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.4287870886065299</v>
+        <v>-1.5431714426528025</v>
       </c>
       <c r="G29" s="0">
-        <v>1.4287870886065299</v>
+        <v>1.5431714426528025</v>
       </c>
       <c r="H29" s="0">
-        <v>18.82121291139347</v>
+        <v>18.706828557347198</v>
       </c>
       <c r="I29" s="0">
-        <v>-1.9287870886065299</v>
+        <v>-2.0431714426528025</v>
       </c>
       <c r="J29" s="0">
-        <v>1.9287870886065299</v>
+        <v>2.0431714426528025</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1716,28 +1716,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>685.61059999999998</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.746522992707845</v>
+        <v>21.756593539975018</v>
       </c>
       <c r="F30" s="0">
-        <v>0.24652299270784539</v>
+        <v>0.2565935399750181</v>
       </c>
       <c r="G30" s="0">
-        <v>0.24652299270784539</v>
+        <v>0.2565935399750181</v>
       </c>
       <c r="H30" s="0">
-        <v>21.246522992707845</v>
+        <v>21.256593539975018</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.25347700729215461</v>
+        <v>-0.2434064600249819</v>
       </c>
       <c r="J30" s="0">
-        <v>0.25347700729215461</v>
+        <v>0.2434064600249819</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>683.32539999999995</v>
+        <v>687.38679999999999</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.681005330404282</v>
+        <v>21.707005586271581</v>
       </c>
       <c r="F31" s="0">
-        <v>2.1810053304042825</v>
+        <v>2.2070055862715812</v>
       </c>
       <c r="G31" s="0">
-        <v>2.1810053304042825</v>
+        <v>2.2070055862715812</v>
       </c>
       <c r="H31" s="0">
-        <v>21.181005330404282</v>
+        <v>21.207005586271581</v>
       </c>
       <c r="I31" s="0">
-        <v>1.6810053304042825</v>
+        <v>1.7070055862715812</v>
       </c>
       <c r="J31" s="0">
-        <v>1.6810053304042825</v>
+        <v>1.7070055862715812</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1804,28 +1804,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>669.30840000000001</v>
+        <v>664.20730000000003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.299533197008451</v>
+        <v>21.055870945864378</v>
       </c>
       <c r="F32" s="0">
-        <v>1.7995331970084507</v>
+        <v>1.5558709458643776</v>
       </c>
       <c r="G32" s="0">
-        <v>1.7995331970084507</v>
+        <v>1.5558709458643776</v>
       </c>
       <c r="H32" s="0">
-        <v>20.799533197008451</v>
+        <v>20.555870945864378</v>
       </c>
       <c r="I32" s="0">
-        <v>1.2995331970084507</v>
+        <v>1.0558709458643776</v>
       </c>
       <c r="J32" s="0">
-        <v>1.2995331970084507</v>
+        <v>1.0558709458643776</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1848,28 +1848,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>712.56219999999996</v>
+        <v>700.82140000000004</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>22.151259540367867</v>
+        <v>21.777900083906982</v>
       </c>
       <c r="F33" s="0">
-        <v>1.1512595403678674</v>
+        <v>0.77790008390698162</v>
       </c>
       <c r="G33" s="0">
-        <v>1.1512595403678674</v>
+        <v>0.77790008390698162</v>
       </c>
       <c r="H33" s="0">
-        <v>21.651259540367867</v>
+        <v>21.277900083906982</v>
       </c>
       <c r="I33" s="0">
-        <v>0.65125954036786737</v>
+        <v>0.27790008390698162</v>
       </c>
       <c r="J33" s="0">
-        <v>0.65125954036786737</v>
+        <v>0.27790008390698162</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>1</v>
@@ -1892,28 +1892,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.39670000000001</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.095367644267856</v>
+        <v>19.971990734739151</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.15463235573214362</v>
+        <v>-0.27800926526084879</v>
       </c>
       <c r="G34" s="0">
-        <v>0.15463235573214362</v>
+        <v>0.27800926526084879</v>
       </c>
       <c r="H34" s="0">
-        <v>19.595367644267856</v>
+        <v>19.471990734739151</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.65463235573214362</v>
+        <v>-0.77800926526084879</v>
       </c>
       <c r="J34" s="0">
-        <v>0.65463235573214362</v>
+        <v>0.77800926526084879</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>622.68050000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.425428722838831</v>
+        <v>20.176862184813786</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.0745712771611693</v>
+        <v>-1.3231378151862145</v>
       </c>
       <c r="G35" s="0">
-        <v>1.0745712771611693</v>
+        <v>1.3231378151862145</v>
       </c>
       <c r="H35" s="0">
-        <v>19.925428722838831</v>
+        <v>19.676862184813786</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.5745712771611693</v>
+        <v>-1.8231378151862145</v>
       </c>
       <c r="J35" s="0">
-        <v>1.5745712771611693</v>
+        <v>1.8231378151862145</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1980,31 +1980,31 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>601.95100000000002</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.016501977641706</v>
+        <v>19.939926237649182</v>
       </c>
       <c r="F36" s="0">
-        <v>0.51650197764170613</v>
+        <v>0.43992623764918193</v>
       </c>
       <c r="G36" s="0">
-        <v>0.51650197764170613</v>
+        <v>0.43992623764918193</v>
       </c>
       <c r="H36" s="0">
-        <v>19.516501977641706</v>
+        <v>19.439926237649182</v>
       </c>
       <c r="I36" s="0">
-        <v>0.016501977641706134</v>
+        <v>-0.060073762350818072</v>
       </c>
       <c r="J36" s="0">
-        <v>0.016501977641706134</v>
+        <v>0.060073762350818072</v>
       </c>
       <c r="K36" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="0">
         <v>1</v>
@@ -2024,28 +2024,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>726.80799999999999</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.462789781250276</v>
+        <v>22.819321994016495</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.5372102187497241</v>
+        <v>-2.1806780059835056</v>
       </c>
       <c r="G37" s="0">
-        <v>2.5372102187497241</v>
+        <v>2.1806780059835056</v>
       </c>
       <c r="H37" s="0">
-        <v>21.962789781250276</v>
+        <v>22.319321994016495</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.0372102187497241</v>
+        <v>-2.6806780059835056</v>
       </c>
       <c r="J37" s="0">
-        <v>3.0372102187497241</v>
+        <v>2.6806780059835056</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>599.73789999999997</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.768081102893305</v>
+        <v>19.691490872558351</v>
       </c>
       <c r="F38" s="0">
-        <v>0.768081102893305</v>
+        <v>0.69149087255835085</v>
       </c>
       <c r="G38" s="0">
-        <v>0.768081102893305</v>
+        <v>0.69149087255835085</v>
       </c>
       <c r="H38" s="0">
-        <v>19.268081102893305</v>
+        <v>19.191490872558351</v>
       </c>
       <c r="I38" s="0">
-        <v>0.268081102893305</v>
+        <v>0.19149087255835085</v>
       </c>
       <c r="J38" s="0">
-        <v>0.268081102893305</v>
+        <v>0.19149087255835085</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2112,28 +2112,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>700.04589999999996</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>22.113155669747396</v>
+        <v>22.006536419025565</v>
       </c>
       <c r="F39" s="0">
-        <v>3.1131556697473961</v>
+        <v>3.006536419025565</v>
       </c>
       <c r="G39" s="0">
-        <v>3.1131556697473961</v>
+        <v>3.006536419025565</v>
       </c>
       <c r="H39" s="0">
-        <v>21.613155669747396</v>
+        <v>21.506536419025565</v>
       </c>
       <c r="I39" s="0">
-        <v>2.6131556697473961</v>
+        <v>2.506536419025565</v>
       </c>
       <c r="J39" s="0">
-        <v>2.6131556697473961</v>
+        <v>2.506536419025565</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2156,28 +2156,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>776.98199999999997</v>
+        <v>762.38530000000003</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>24.714301558676652</v>
+        <v>24.539626086625837</v>
       </c>
       <c r="F40" s="0">
-        <v>3.7143015586766523</v>
+        <v>3.5396260866258373</v>
       </c>
       <c r="G40" s="0">
-        <v>3.7143015586766523</v>
+        <v>3.5396260866258373</v>
       </c>
       <c r="H40" s="0">
-        <v>24.214301558676652</v>
+        <v>24.039626086625837</v>
       </c>
       <c r="I40" s="0">
-        <v>3.2143015586766523</v>
+        <v>3.0396260866258373</v>
       </c>
       <c r="J40" s="0">
-        <v>3.2143015586766523</v>
+        <v>3.0396260866258373</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2200,28 +2200,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>673.32410000000004</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.405122474971378</v>
+        <v>21.273012910900665</v>
       </c>
       <c r="F41" s="0">
-        <v>0.90512247497137821</v>
+        <v>0.77301291090066471</v>
       </c>
       <c r="G41" s="0">
-        <v>0.90512247497137821</v>
+        <v>0.77301291090066471</v>
       </c>
       <c r="H41" s="0">
-        <v>20.905122474971378</v>
+        <v>20.773012910900665</v>
       </c>
       <c r="I41" s="0">
-        <v>0.40512247497137821</v>
+        <v>0.27301291090066471</v>
       </c>
       <c r="J41" s="0">
-        <v>0.40512247497137821</v>
+        <v>0.27301291090066471</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2244,28 +2244,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>526.36469999999997</v>
+        <v>523.23350000000005</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.280698089999582</v>
+        <v>19.170024293901879</v>
       </c>
       <c r="F42" s="0">
-        <v>0.030698089999582123</v>
+        <v>-0.079975706098121435</v>
       </c>
       <c r="G42" s="0">
-        <v>0.030698089999582123</v>
+        <v>0.079975706098121435</v>
       </c>
       <c r="H42" s="0">
-        <v>18.780698089999582</v>
+        <v>18.670024293901879</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.46930191000041788</v>
+        <v>-0.57997570609812144</v>
       </c>
       <c r="J42" s="0">
-        <v>0.46930191000041788</v>
+        <v>0.57997570609812144</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2288,28 +2288,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>586.85530000000006</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.653284439610474</v>
+        <v>19.639453877565202</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.34671556038952645</v>
+        <v>-0.36054612243479767</v>
       </c>
       <c r="G43" s="0">
-        <v>0.34671556038952645</v>
+        <v>0.36054612243479767</v>
       </c>
       <c r="H43" s="0">
-        <v>19.153284439610474</v>
+        <v>19.139453877565202</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.84671556038952644</v>
+        <v>-0.86054612243479767</v>
       </c>
       <c r="J43" s="0">
-        <v>0.84671556038952644</v>
+        <v>0.86054612243479767</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2332,28 +2332,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>663.21749999999997</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.228512240278569</v>
+        <v>21.067957291586971</v>
       </c>
       <c r="F44" s="0">
-        <v>1.2285122402785689</v>
+        <v>1.0679572915869713</v>
       </c>
       <c r="G44" s="0">
-        <v>1.2285122402785689</v>
+        <v>1.0679572915869713</v>
       </c>
       <c r="H44" s="0">
-        <v>20.728512240278569</v>
+        <v>20.567957291586971</v>
       </c>
       <c r="I44" s="0">
-        <v>0.72851224027856887</v>
+        <v>0.56795729158697128</v>
       </c>
       <c r="J44" s="0">
-        <v>0.72851224027856887</v>
+        <v>0.56795729158697128</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2376,28 +2376,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>582.90459999999996</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.573358861773311</v>
+        <v>19.820279792266362</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.42664113822668881</v>
+        <v>-0.17972020773363795</v>
       </c>
       <c r="G45" s="0">
-        <v>0.42664113822668881</v>
+        <v>0.17972020773363795</v>
       </c>
       <c r="H45" s="0">
-        <v>19.073358861773311</v>
+        <v>19.320279792266362</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.92664113822668881</v>
+        <v>-0.67972020773363795</v>
       </c>
       <c r="J45" s="0">
-        <v>0.92664113822668881</v>
+        <v>0.67972020773363795</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2420,28 +2420,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>732.64890000000003</v>
+        <v>725.4751</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>22.872264714902272</v>
+        <v>22.742651388633707</v>
       </c>
       <c r="F46" s="0">
-        <v>0.87226471490227198</v>
+        <v>0.74265138863370694</v>
       </c>
       <c r="G46" s="0">
-        <v>0.87226471490227198</v>
+        <v>0.74265138863370694</v>
       </c>
       <c r="H46" s="0">
-        <v>22.372264714902272</v>
+        <v>22.242651388633707</v>
       </c>
       <c r="I46" s="0">
-        <v>0.37226471490227198</v>
+        <v>0.24265138863370694</v>
       </c>
       <c r="J46" s="0">
-        <v>0.37226471490227198</v>
+        <v>0.24265138863370694</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>1</v>
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>704.21619999999996</v>
+        <v>700.72990000000004</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>22.212955580169456</v>
+        <v>22.055238789784479</v>
       </c>
       <c r="F47" s="0">
-        <v>0.21295558016945648</v>
+        <v>0.055238789784478826</v>
       </c>
       <c r="G47" s="0">
-        <v>0.21295558016945648</v>
+        <v>0.055238789784478826</v>
       </c>
       <c r="H47" s="0">
-        <v>21.712955580169456</v>
+        <v>21.555238789784479</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.28704441983054352</v>
+        <v>-0.44476121021552117</v>
       </c>
       <c r="J47" s="0">
-        <v>0.28704441983054352</v>
+        <v>0.44476121021552117</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2508,28 +2508,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>707.67989999999998</v>
+        <v>697.40779999999995</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.868145283351971</v>
+        <v>21.679559503888815</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.1318547166480286</v>
+        <v>-1.3204404961111855</v>
       </c>
       <c r="G48" s="0">
-        <v>1.1318547166480286</v>
+        <v>1.3204404961111855</v>
       </c>
       <c r="H48" s="0">
-        <v>21.368145283351971</v>
+        <v>21.179559503888815</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.6318547166480286</v>
+        <v>-1.8204404961111855</v>
       </c>
       <c r="J48" s="0">
-        <v>1.6318547166480286</v>
+        <v>1.8204404961111855</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2552,28 +2552,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>666.81700000000001</v>
+        <v>664.56500000000005</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.831053281467717</v>
+        <v>20.865982691968274</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.9189467185322826</v>
+        <v>-0.8840173080317264</v>
       </c>
       <c r="G49" s="0">
-        <v>0.9189467185322826</v>
+        <v>0.8840173080317264</v>
       </c>
       <c r="H49" s="0">
-        <v>20.331053281467717</v>
+        <v>20.365982691968274</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.4189467185322826</v>
+        <v>-1.3840173080317264</v>
       </c>
       <c r="J49" s="0">
-        <v>1.4189467185322826</v>
+        <v>1.3840173080317264</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2596,28 +2596,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>688.77390000000003</v>
+        <v>689.15930000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.551145842457235</v>
+        <v>21.516553999645911</v>
       </c>
       <c r="F50" s="0">
-        <v>0.051145842457234636</v>
+        <v>0.016553999645910977</v>
       </c>
       <c r="G50" s="0">
-        <v>0.051145842457234636</v>
+        <v>0.016553999645910977</v>
       </c>
       <c r="H50" s="0">
-        <v>21.051145842457235</v>
+        <v>21.016553999645911</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.44885415754276537</v>
+        <v>-0.48344600035408902</v>
       </c>
       <c r="J50" s="0">
-        <v>0.44885415754276537</v>
+        <v>0.48344600035408902</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2640,28 +2640,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>615.82560000000001</v>
+        <v>610.64480000000003</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.190776622533747</v>
+        <v>20.058369902151345</v>
       </c>
       <c r="F51" s="0">
-        <v>0.99077662253374754</v>
+        <v>0.85836990215134534</v>
       </c>
       <c r="G51" s="0">
-        <v>0.99077662253374754</v>
+        <v>0.85836990215134534</v>
       </c>
       <c r="H51" s="0">
-        <v>19.690776622533747</v>
+        <v>19.558369902151345</v>
       </c>
       <c r="I51" s="0">
-        <v>0.49077662253374754</v>
+        <v>0.35836990215134534</v>
       </c>
       <c r="J51" s="0">
-        <v>0.49077662253374754</v>
+        <v>0.35836990215134534</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2684,28 +2684,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>568.91740000000004</v>
+        <v>576.71630000000005</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.451856118416636</v>
+        <v>19.80262478566274</v>
       </c>
       <c r="F52" s="0">
-        <v>1.9518561184166359</v>
+        <v>2.30262478566274</v>
       </c>
       <c r="G52" s="0">
-        <v>1.9518561184166359</v>
+        <v>2.30262478566274</v>
       </c>
       <c r="H52" s="0">
-        <v>18.951856118416636</v>
+        <v>19.30262478566274</v>
       </c>
       <c r="I52" s="0">
-        <v>1.4518561184166359</v>
+        <v>1.80262478566274</v>
       </c>
       <c r="J52" s="0">
-        <v>1.4518561184166359</v>
+        <v>1.80262478566274</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2728,28 +2728,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>594.03499999999997</v>
+        <v>598.05470000000003</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.952856754467639</v>
+        <v>19.968049878729598</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5528567544676406</v>
+        <v>1.5680498787295996</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5528567544676406</v>
+        <v>1.5680498787295996</v>
       </c>
       <c r="H53" s="0">
-        <v>19.452856754467639</v>
+        <v>19.468049878729598</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0528567544676406</v>
+        <v>1.0680498787295996</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0528567544676406</v>
+        <v>1.0680498787295996</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2772,28 +2772,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>566.51940000000002</v>
+        <v>573.06939999999997</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.534708614094726</v>
+        <v>19.600302790129582</v>
       </c>
       <c r="F54" s="0">
-        <v>0.53470861409472548</v>
+        <v>0.60030279012958232</v>
       </c>
       <c r="G54" s="0">
-        <v>0.53470861409472548</v>
+        <v>0.60030279012958232</v>
       </c>
       <c r="H54" s="0">
-        <v>19.034708614094726</v>
+        <v>19.100302790129582</v>
       </c>
       <c r="I54" s="0">
-        <v>0.034708614094725476</v>
+        <v>0.10030279012958232</v>
       </c>
       <c r="J54" s="0">
-        <v>0.034708614094725476</v>
+        <v>0.10030279012958232</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2816,28 +2816,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>614.26739999999995</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>19.940101280553549</v>
+        <v>19.813604622050985</v>
       </c>
       <c r="F55" s="0">
-        <v>0.44010128055354869</v>
+        <v>0.31360462205098472</v>
       </c>
       <c r="G55" s="0">
-        <v>0.44010128055354869</v>
+        <v>0.31360462205098472</v>
       </c>
       <c r="H55" s="0">
-        <v>19.440101280553549</v>
+        <v>19.313604622050985</v>
       </c>
       <c r="I55" s="0">
-        <v>-0.05989871944645131</v>
+        <v>-0.18639537794901529</v>
       </c>
       <c r="J55" s="0">
-        <v>0.05989871944645131</v>
+        <v>0.18639537794901529</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>0</v>
@@ -2860,28 +2860,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>717.47789999999998</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>22.526024925778771</v>
+        <v>22.063497730567878</v>
       </c>
       <c r="F56" s="0">
-        <v>2.0260249257787706</v>
+        <v>1.5634977305678781</v>
       </c>
       <c r="G56" s="0">
-        <v>2.0260249257787706</v>
+        <v>1.5634977305678781</v>
       </c>
       <c r="H56" s="0">
-        <v>22.026024925778771</v>
+        <v>21.563497730567878</v>
       </c>
       <c r="I56" s="0">
-        <v>1.5260249257787706</v>
+        <v>1.0634977305678781</v>
       </c>
       <c r="J56" s="0">
-        <v>1.5260249257787706</v>
+        <v>1.0634977305678781</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2904,28 +2904,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>656.12369999999999</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.745218702182413</v>
+        <v>20.55227348042953</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.25478129781758696</v>
+        <v>-0.44772651957046961</v>
       </c>
       <c r="G57" s="0">
-        <v>0.25478129781758696</v>
+        <v>0.44772651957046961</v>
       </c>
       <c r="H57" s="0">
-        <v>20.245218702182413</v>
+        <v>20.05227348042953</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.75478129781758696</v>
+        <v>-0.94772651957046961</v>
       </c>
       <c r="J57" s="0">
-        <v>0.75478129781758696</v>
+        <v>0.94772651957046961</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>713.17060000000004</v>
+        <v>713.38980000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>22.146789715511915</v>
+        <v>22.220901589190426</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.3532102844880853</v>
+        <v>-1.2790984108095742</v>
       </c>
       <c r="G58" s="0">
-        <v>1.3532102844880853</v>
+        <v>1.2790984108095742</v>
       </c>
       <c r="H58" s="0">
-        <v>21.646789715511915</v>
+        <v>21.720901589190426</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.8532102844880853</v>
+        <v>-1.7790984108095742</v>
       </c>
       <c r="J58" s="0">
-        <v>1.8532102844880853</v>
+        <v>1.7790984108095742</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2992,28 +2992,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>675.12120000000004</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.453354647770933</v>
+        <v>21.259346511125521</v>
       </c>
       <c r="F59" s="0">
-        <v>0.95335464777093293</v>
+        <v>0.75934651112552132</v>
       </c>
       <c r="G59" s="0">
-        <v>0.95335464777093293</v>
+        <v>0.75934651112552132</v>
       </c>
       <c r="H59" s="0">
-        <v>20.953354647770933</v>
+        <v>20.759346511125521</v>
       </c>
       <c r="I59" s="0">
-        <v>0.45335464777093293</v>
+        <v>0.25934651112552132</v>
       </c>
       <c r="J59" s="0">
-        <v>0.45335464777093293</v>
+        <v>0.25934651112552132</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3036,28 +3036,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>689.68129999999997</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.576230421697272</v>
+        <v>21.785222797158827</v>
       </c>
       <c r="F60" s="0">
-        <v>0.076230421697271566</v>
+        <v>0.28522279715882704</v>
       </c>
       <c r="G60" s="0">
-        <v>0.076230421697271566</v>
+        <v>0.28522279715882704</v>
       </c>
       <c r="H60" s="0">
-        <v>21.076230421697272</v>
+        <v>21.285222797158827</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.42376957830272843</v>
+        <v>-0.21477720284117297</v>
       </c>
       <c r="J60" s="0">
-        <v>0.42376957830272843</v>
+        <v>0.21477720284117297</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>646.9873</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.756243671378353</v>
+        <v>20.810912180688522</v>
       </c>
       <c r="F61" s="0">
-        <v>0.75624367137835336</v>
+        <v>0.810912180688522</v>
       </c>
       <c r="G61" s="0">
-        <v>0.75624367137835336</v>
+        <v>0.810912180688522</v>
       </c>
       <c r="H61" s="0">
-        <v>20.256243671378353</v>
+        <v>20.310912180688522</v>
       </c>
       <c r="I61" s="0">
-        <v>0.25624367137835335</v>
+        <v>0.310912180688522</v>
       </c>
       <c r="J61" s="0">
-        <v>0.25624367137835335</v>
+        <v>0.310912180688522</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3124,28 +3124,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>680.14350000000002</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.408636055750218</v>
+        <v>21.704768523539503</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.5913639442497818</v>
+        <v>-1.2952314764604971</v>
       </c>
       <c r="G62" s="0">
-        <v>1.5913639442497818</v>
+        <v>1.2952314764604971</v>
       </c>
       <c r="H62" s="0">
-        <v>20.908636055750218</v>
+        <v>21.204768523539503</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.0913639442497818</v>
+        <v>-1.7952314764604971</v>
       </c>
       <c r="J62" s="0">
-        <v>2.0913639442497818</v>
+        <v>1.7952314764604971</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3168,28 +3168,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>675.0444</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.510595887035915</v>
+        <v>21.37357006616736</v>
       </c>
       <c r="F63" s="0">
-        <v>0.010595887035915297</v>
+        <v>-0.12642993383263956</v>
       </c>
       <c r="G63" s="0">
-        <v>0.010595887035915297</v>
+        <v>0.12642993383263956</v>
       </c>
       <c r="H63" s="0">
-        <v>21.010595887035915</v>
+        <v>20.87357006616736</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.4894041129640847</v>
+        <v>-0.62642993383263956</v>
       </c>
       <c r="J63" s="0">
-        <v>0.4894041129640847</v>
+        <v>0.62642993383263956</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3212,28 +3212,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>638.85119999999995</v>
+        <v>643.54809999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.343204667934987</v>
+        <v>20.304937955636362</v>
       </c>
       <c r="F64" s="0">
-        <v>-2.1567953320650126</v>
+        <v>-2.1950620443636382</v>
       </c>
       <c r="G64" s="0">
-        <v>2.1567953320650126</v>
+        <v>2.1950620443636382</v>
       </c>
       <c r="H64" s="0">
-        <v>19.843204667934987</v>
+        <v>19.804937955636362</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.6567953320650126</v>
+        <v>-2.6950620443636382</v>
       </c>
       <c r="J64" s="0">
-        <v>2.6567953320650126</v>
+        <v>2.6950620443636382</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3256,28 +3256,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>595.31380000000001</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>19.902752520007834</v>
+        <v>19.905064671043469</v>
       </c>
       <c r="F65" s="0">
-        <v>0.65275252000783368</v>
+        <v>0.6550646710434691</v>
       </c>
       <c r="G65" s="0">
-        <v>0.65275252000783368</v>
+        <v>0.6550646710434691</v>
       </c>
       <c r="H65" s="0">
-        <v>19.402752520007834</v>
+        <v>19.405064671043469</v>
       </c>
       <c r="I65" s="0">
-        <v>0.15275252000783368</v>
+        <v>0.15506467104346911</v>
       </c>
       <c r="J65" s="0">
-        <v>0.15275252000783368</v>
+        <v>0.15506467104346911</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3300,28 +3300,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>698.0498</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.437466294229477</v>
+        <v>22.05831600238259</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.0625337057705231</v>
+        <v>-1.4416839976174103</v>
       </c>
       <c r="G66" s="0">
-        <v>2.0625337057705231</v>
+        <v>1.4416839976174103</v>
       </c>
       <c r="H66" s="0">
-        <v>20.937466294229477</v>
+        <v>21.55831600238259</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.5625337057705231</v>
+        <v>-1.9416839976174103</v>
       </c>
       <c r="J66" s="0">
-        <v>2.5625337057705231</v>
+        <v>1.9416839976174103</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3344,28 +3344,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>634.08339999999998</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.56665683524735</v>
+        <v>20.40919578501758</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.93334316475264956</v>
+        <v>-1.0908042149824198</v>
       </c>
       <c r="G67" s="0">
-        <v>0.93334316475264956</v>
+        <v>1.0908042149824198</v>
       </c>
       <c r="H67" s="0">
-        <v>20.06665683524735</v>
+        <v>19.90919578501758</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.4333431647526496</v>
+        <v>-1.5908042149824198</v>
       </c>
       <c r="J67" s="0">
-        <v>1.4333431647526496</v>
+        <v>1.5908042149824198</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>578.7296</v>
+        <v>581.15859999999998</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.506726354918918</v>
+        <v>19.828512518237506</v>
       </c>
       <c r="F68" s="0">
-        <v>0.50672635491891782</v>
+        <v>0.82851251823750616</v>
       </c>
       <c r="G68" s="0">
-        <v>0.50672635491891782</v>
+        <v>0.82851251823750616</v>
       </c>
       <c r="H68" s="0">
-        <v>19.006726354918918</v>
+        <v>19.328512518237506</v>
       </c>
       <c r="I68" s="0">
-        <v>0.0067263549189178207</v>
+        <v>0.32851251823750616</v>
       </c>
       <c r="J68" s="0">
-        <v>0.0067263549189178207</v>
+        <v>0.32851251823750616</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3470,16 +3470,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.127</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.4119999999999999</v>
+        <v>1.357</v>
       </c>
       <c r="D2" s="0">
-        <v>0.378</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>0.017999999999999999</v>
+        <v>-0.0060000000000000001</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3489,22 +3489,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="C3" s="0">
-        <v>0.025999999999999999</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>0.017999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="E3" s="0">
-        <v>0.039</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G3" s="0">
-        <v>2</v>
+        <v>0.69999999999999996</v>
       </c>
     </row>
     <row r="4">
@@ -3523,18 +3523,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.171</v>
+        <v>1.127</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.48199999999999999</v>
+        <v>-0.50600000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>53.399999999999999</v>
+        <v>53</v>
       </c>
       <c r="G5" s="0">
-        <v>41.5</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3542,16 +3542,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.1200000000000001</v>
+        <v>1.105</v>
       </c>
       <c r="C6" s="0">
-        <v>1.4039999999999999</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>0.38200000000000001</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="E6" s="0">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3561,15 +3561,15 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.167</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.47999999999999998</v>
+        <v>-0.48599999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>53.700000000000003</v>
+        <v>50.700000000000003</v>
       </c>
       <c r="G7" s="0">
         <v>38.799999999999997</v>
@@ -3680,13 +3680,13 @@
         <v>111</v>
       </c>
       <c r="B2" s="0">
-        <v>9.0012000000000008</v>
+        <v>8.7514000000000003</v>
       </c>
       <c r="C2" s="0">
-        <v>1.6853</v>
+        <v>1.6551</v>
       </c>
       <c r="D2" s="0">
-        <v>5.3410000000000002</v>
+        <v>5.2880000000000003</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3697,13 +3697,13 @@
         <v>112</v>
       </c>
       <c r="B3" s="0">
-        <v>0.018499999999999999</v>
+        <v>0.0189</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025999999999999999</v>
+        <v>0.0025000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>7.1459999999999999</v>
+        <v>7.4279999999999999</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
